--- a/artfynd/A 69012-2021 artfynd.xlsx
+++ b/artfynd/A 69012-2021 artfynd.xlsx
@@ -1805,7 +1805,7 @@
         <v>112795625</v>
       </c>
       <c r="B13" t="n">
-        <v>91872</v>
+        <v>91881</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69012-2021 artfynd.xlsx
+++ b/artfynd/A 69012-2021 artfynd.xlsx
@@ -1805,7 +1805,7 @@
         <v>112795625</v>
       </c>
       <c r="B13" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69012-2021 artfynd.xlsx
+++ b/artfynd/A 69012-2021 artfynd.xlsx
@@ -1805,7 +1805,7 @@
         <v>112795625</v>
       </c>
       <c r="B13" t="n">
-        <v>91882</v>
+        <v>91887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69012-2021 artfynd.xlsx
+++ b/artfynd/A 69012-2021 artfynd.xlsx
@@ -1805,7 +1805,7 @@
         <v>112795625</v>
       </c>
       <c r="B13" t="n">
-        <v>91887</v>
+        <v>91889</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
